--- a/news_daily/2026-09-11.xlsx
+++ b/news_daily/2026-09-11.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BL14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1169,6 +1197,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1331,6 +1363,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1501,6 +1537,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1671,6 +1711,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1833,6 +1877,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1995,6 +2043,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2035,7 +2087,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -2045,13 +2097,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -2091,7 +2147,7 @@
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
@@ -2100,7 +2156,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>732ae4b5d9b342c89ff27154e72a5fe3</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>fd73760f4e38556c3bbe03f3</t>
@@ -2121,7 +2181,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -2157,6 +2221,22 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2207,13 +2287,17 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -2262,7 +2346,11 @@
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>67620b9a1b954e7c8565b0a8f8039c6f</t>
+        </is>
+      </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>079be941c24ec300cd9a2e82</t>
@@ -2283,7 +2371,11 @@
       <c r="AL10" s="4" t="inlineStr"/>
       <c r="AM10" s="4" t="inlineStr"/>
       <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="4" t="inlineStr"/>
       <c r="AQ10" s="4" t="inlineStr"/>
       <c r="AR10" s="4" t="inlineStr"/>
@@ -2319,6 +2411,18 @@
         </is>
       </c>
       <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BI10" s="4" t="inlineStr"/>
+      <c r="BJ10" s="4" t="inlineStr"/>
+      <c r="BK10" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2481,6 +2585,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2531,13 +2639,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -2586,7 +2698,11 @@
         </is>
       </c>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>0fb04fad69ea4456984055445c870532</t>
+        </is>
+      </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>22cb955c9ccad038fbab7154</t>
@@ -2607,7 +2723,11 @@
       <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="inlineStr"/>
       <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="inlineStr"/>
@@ -2651,6 +2771,18 @@
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2701,13 +2833,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2756,7 +2892,11 @@
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>f51e7524e8094a9facd43fdf1ea4db0f</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>0a92ba29700c0403216434d3</t>
@@ -2777,7 +2917,11 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
       <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="inlineStr"/>
@@ -2813,6 +2957,18 @@
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2863,13 +3019,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2918,7 +3078,11 @@
         </is>
       </c>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>398bca0c7fd74b008db6e34b6bf14525</t>
+        </is>
+      </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>079be941c24ec300cd9a2e82</t>
@@ -2939,7 +3103,11 @@
       <c r="AL14" s="4" t="inlineStr"/>
       <c r="AM14" s="4" t="inlineStr"/>
       <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="4" t="inlineStr"/>
       <c r="AQ14" s="4" t="inlineStr"/>
       <c r="AR14" s="4" t="inlineStr"/>
@@ -2983,9 +3151,21 @@
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH14"/>
+  <autoFilter ref="A1:BL14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2996,7 +3176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3059,6 +3239,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3360,6 +3544,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -3532,6 +3736,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3702,6 +3910,10 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3864,6 +4076,10 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4034,6 +4250,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4204,6 +4424,10 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4366,6 +4590,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4406,7 +4634,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -4416,13 +4644,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -4462,7 +4694,7 @@
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
@@ -4471,7 +4703,11 @@
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>732ae4b5d9b342c89ff27154e72a5fe3</t>
+        </is>
+      </c>
       <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>fd73760f4e38556c3bbe03f3</t>
@@ -4492,7 +4728,11 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -4528,6 +4768,22 @@
         </is>
       </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4578,13 +4834,17 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -4633,7 +4893,11 @@
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>67620b9a1b954e7c8565b0a8f8039c6f</t>
+        </is>
+      </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>079be941c24ec300cd9a2e82</t>
@@ -4654,7 +4918,11 @@
       <c r="AL9" s="4" t="inlineStr"/>
       <c r="AM9" s="4" t="inlineStr"/>
       <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="4" t="inlineStr"/>
       <c r="AQ9" s="4" t="inlineStr"/>
       <c r="AR9" s="4" t="inlineStr"/>
@@ -4690,6 +4958,18 @@
         </is>
       </c>
       <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4852,6 +5132,10 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4902,13 +5186,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -4957,7 +5245,11 @@
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>0fb04fad69ea4456984055445c870532</t>
+        </is>
+      </c>
       <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>22cb955c9ccad038fbab7154</t>
@@ -4978,7 +5270,11 @@
       <c r="AL11" s="4" t="inlineStr"/>
       <c r="AM11" s="4" t="inlineStr"/>
       <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="4" t="inlineStr"/>
       <c r="AQ11" s="4" t="inlineStr"/>
       <c r="AR11" s="4" t="inlineStr"/>
@@ -5022,6 +5318,18 @@
         </is>
       </c>
       <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -5072,13 +5380,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -5127,7 +5439,11 @@
         </is>
       </c>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>f51e7524e8094a9facd43fdf1ea4db0f</t>
+        </is>
+      </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>0a92ba29700c0403216434d3</t>
@@ -5148,7 +5464,11 @@
       <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="inlineStr"/>
       <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="inlineStr"/>
@@ -5184,6 +5504,18 @@
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -5234,13 +5566,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -5289,7 +5625,11 @@
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>398bca0c7fd74b008db6e34b6bf14525</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>079be941c24ec300cd9a2e82</t>
@@ -5310,7 +5650,11 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
       <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="inlineStr"/>
@@ -5354,9 +5698,21 @@
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5367,7 +5723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5430,6 +5786,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5733,9 +6093,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5746,7 +6126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5809,6 +6189,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6112,9 +6496,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6125,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6175,134 +6579,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -6312,46 +6716,80 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="3" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="inlineStr"/>
       <c r="Z2" s="3" t="inlineStr"/>
@@ -6360,12 +6798,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6375,90 +6813,94 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6468,94 +6910,94 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6563,89 +7005,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-11.xlsx
+++ b/news_daily/2026-09-11.xlsx
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f7a4de3d3d4d4ceab6a1fd9d6acf6b2d</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>93b4c317b616fb0ce364acac</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1025,8 +1037,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1077,13 +1097,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1132,7 +1156,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>3b00aeb696b7419e9e8ad5d3b1493085</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>91dec08e5a2d3407c670d64f</t>
@@ -1153,7 +1181,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1199,8 +1231,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1251,13 +1291,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1306,7 +1350,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>0fe0fa0948ff400a925181e6a4d046a1</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>83ff92f5a595e3e78f1c211c</t>
@@ -1327,7 +1375,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1365,8 +1417,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1417,13 +1477,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1472,7 +1536,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>22566ea9af314bca97b1a53642c0c65b</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>458c05950cb44c9b30fc4303</t>
@@ -1493,7 +1561,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1539,8 +1611,16 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1591,13 +1671,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1646,7 +1730,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>af2b56aeba4f49ce949d0f1e7e26d43c</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>6f96b076048457e21eaac432</t>
@@ -1667,7 +1755,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1713,8 +1805,16 @@
       <c r="BH6" s="2" t="inlineStr"/>
       <c r="BI6" s="2" t="inlineStr"/>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1931,13 +2031,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1986,7 +2090,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>6b70230e899a4624892490261a655a39</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>bf9c56c1693a9d546abd230b</t>
@@ -2007,7 +2115,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2045,8 +2157,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2473,13 +2593,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2528,7 +2652,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>5da715afe10c45bab185064f17ddfea4</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>1e71da32c0ba6f40643af3e1</t>
@@ -2549,7 +2677,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2587,8 +2719,16 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3616,13 +3756,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -3671,7 +3815,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f7a4de3d3d4d4ceab6a1fd9d6acf6b2d</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>93b4c317b616fb0ce364acac</t>
@@ -3692,7 +3840,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -3738,8 +3890,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3790,13 +3950,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -3845,7 +4009,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>3b00aeb696b7419e9e8ad5d3b1493085</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>91dec08e5a2d3407c670d64f</t>
@@ -3866,7 +4034,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -3912,8 +4084,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3964,13 +4144,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4019,7 +4203,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>0fe0fa0948ff400a925181e6a4d046a1</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>83ff92f5a595e3e78f1c211c</t>
@@ -4040,7 +4228,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -4078,8 +4270,16 @@
       <c r="BH4" s="2" t="inlineStr"/>
       <c r="BI4" s="2" t="inlineStr"/>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4130,13 +4330,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4185,7 +4389,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>22566ea9af314bca97b1a53642c0c65b</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>458c05950cb44c9b30fc4303</t>
@@ -4206,7 +4414,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -4252,8 +4464,16 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4304,13 +4524,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4359,7 +4583,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>af2b56aeba4f49ce949d0f1e7e26d43c</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>6f96b076048457e21eaac432</t>
@@ -4380,7 +4608,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -4426,8 +4658,16 @@
       <c r="BH6" s="2" t="inlineStr"/>
       <c r="BI6" s="2" t="inlineStr"/>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4478,13 +4718,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,7 +4777,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>6b70230e899a4624892490261a655a39</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>bf9c56c1693a9d546abd230b</t>
@@ -4554,7 +4802,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -4592,8 +4844,16 @@
       <c r="BH7" s="2" t="inlineStr"/>
       <c r="BI7" s="2" t="inlineStr"/>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -5020,13 +5280,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5075,7 +5339,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>5da715afe10c45bab185064f17ddfea4</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>1e71da32c0ba6f40643af3e1</t>
@@ -5096,7 +5364,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -5134,8 +5406,16 @@
       <c r="BH10" s="2" t="inlineStr"/>
       <c r="BI10" s="2" t="inlineStr"/>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">

--- a/news_daily/2026-09-11.xlsx
+++ b/news_daily/2026-09-11.xlsx
@@ -1850,28 +1850,32 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1920,7 +1924,11 @@
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>66b1db2308e54ade8f6fc1701e1a01db</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>57a6dfaefe4679e5e45c37fa</t>
@@ -1941,7 +1949,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1977,10 +1989,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
